--- a/Statistics/200m Butterfly_statistics.xlsx
+++ b/Statistics/200m Butterfly_statistics.xlsx
@@ -1206,12 +1206,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Scott Rene Høgenhaug</t>
+          <t>Kristoffer Loeng</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.31,61</t>
+          <t>2.31,57</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21.10.2017</t>
+          <t>04.10.2015</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kristoffer Loeng</t>
+          <t>Scott Rene Høgenhaug</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2.31,57</t>
+          <t>2.31,61</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>04.10.2015</t>
+          <t>21.10.2017</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1591,25 +1591,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.43,91</t>
+          <t>2.43,61</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1626,25 +1626,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Daniel Moen Manriquez</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2.45,26</t>
+          <t>2.43,91</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>23.10.2016</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1661,25 +1661,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bjarne Forfot</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2.46,21</t>
+          <t>2.44,66</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>01.10.2017</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1696,25 +1696,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Daniel Moen Manriquez</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.47,09</t>
+          <t>2.45,26</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>23.10.2016</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1731,25 +1731,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Manith Randula Attanapola</t>
+          <t>Bjarne Forfot</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.49,15</t>
+          <t>2.46,21</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>30.10.2011</t>
+          <t>01.10.2017</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1766,20 +1766,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>David Fjeld</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2.51,97</t>
+          <t>2.47,09</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>07.10.2007</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1801,20 +1801,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Vishnu Sattanathan</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.54,47</t>
+          <t>2.47,52</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1836,25 +1836,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hasith Ransiri Attanapola</t>
+          <t>Manith Randula Attanapola</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.55,38</t>
+          <t>2.49,15</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22.10.2017</t>
+          <t>30.10.2011</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1871,20 +1871,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>David Fjeld</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2.57,49</t>
+          <t>2.51,97</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>07.10.2007</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1906,25 +1906,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Vishnu Sattanathan</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3.01,57</t>
+          <t>2.54,47</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13.03.2011</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1941,25 +1941,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Theodor Solheim</t>
+          <t>Hasith Ransiri Attanapola</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3.02,71</t>
+          <t>2.55,38</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>22.10.2017</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1976,25 +1976,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3.05,90</t>
+          <t>3.01,57</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>13.03.2011</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2011,25 +2011,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Theodor Solheim</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3.07,95</t>
+          <t>3.02,71</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13.03.2011</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2046,25 +2046,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3.15,01</t>
+          <t>3.07,95</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>13.03.2011</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2552,12 +2552,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kristian Volden</t>
+          <t>Christoffer Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.28,14</t>
+          <t>2.28,06</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.05.2016</t>
+          <t>14.06.2015</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2587,12 +2587,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Christoffer Solberg Jørgensen</t>
+          <t>Kristian Volden</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.28,06</t>
+          <t>2.28,14</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14.06.2015</t>
+          <t>28.05.2016</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2937,12 +2937,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bjarne Forfot</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.52,31</t>
+          <t>2.52,25</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>08.07.2017</t>
+          <t>16.06.2024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ankerskogen svømmehall</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2972,12 +2972,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Bjarne Forfot</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.52,25</t>
+          <t>2.52,31</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>16.06.2024</t>
+          <t>08.07.2017</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ankerskogen svømmehall</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3295,7 +3295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4143,20 +4143,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Olea Winnberg</t>
+          <t>Helle Johnsen Selsås</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3.13,18</t>
+          <t>3.09,09</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>28.09.2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4178,25 +4178,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Oline Skjønberg</t>
+          <t>Olea Winnberg</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3.26,20</t>
+          <t>3.13,18</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4213,25 +4213,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chloe Branlat</t>
+          <t>Oline Skjønberg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3.37,04</t>
+          <t>3.26,20</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4248,20 +4248,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Chloe Branlat</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3.40,13</t>
+          <t>3.37,04</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>06.10.2013</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4283,33 +4283,68 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Othelie Annette Høie</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3.40,13</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>160</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>06.10.2013</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>3.55,64</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C30" t="n">
         <v>130</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>19.01.2025</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Trondheim</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Female</t>
         </is>

--- a/Statistics/200m Butterfly_statistics.xlsx
+++ b/Statistics/200m Butterfly_statistics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,12 +1206,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kristoffer Loeng</t>
+          <t>Scott Rene Høgenhaug</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.31,57</t>
+          <t>2.31,61</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>04.10.2015</t>
+          <t>21.10.2017</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Scott Rene Høgenhaug</t>
+          <t>Kristoffer Loeng</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2.31,61</t>
+          <t>2.31,57</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21.10.2017</t>
+          <t>04.10.2015</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1556,12 +1556,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Einar Woldseth</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2.43,01</t>
+          <t>2.43,09</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>07.03.2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1591,25 +1591,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Einar Woldseth</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.43,61</t>
+          <t>2.43,01</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1626,25 +1626,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2.43,91</t>
+          <t>2.43,61</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1661,25 +1661,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2.44,66</t>
+          <t>2.43,91</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1696,25 +1696,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Daniel Moen Manriquez</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.45,26</t>
+          <t>2.44,66</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>23.10.2016</t>
+          <t>24.10.2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1731,25 +1731,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bjarne Forfot</t>
+          <t>Daniel Moen Manriquez</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.46,21</t>
+          <t>2.45,26</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>01.10.2017</t>
+          <t>23.10.2016</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1766,25 +1766,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Bjarne Forfot</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2.47,09</t>
+          <t>2.46,21</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>01.10.2017</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1801,20 +1801,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.47,52</t>
+          <t>2.47,09</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>28.09.2025</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1976,25 +1976,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3.01,57</t>
+          <t>3.18,22</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13.03.2011</t>
+          <t>07.03.2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2011,25 +2011,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Theodor Solheim</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3.02,71</t>
+          <t>3.01,57</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>13.03.2011</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2046,25 +2046,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Theodor Solheim</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3.07,95</t>
+          <t>3.02,71</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13.03.2011</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2081,25 +2081,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>David Csejtey</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3.31,88</t>
+          <t>3.07,95</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>128</v>
+        <v>183</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>13.03.2011</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2116,25 +2116,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Paal Aagaard</t>
+          <t>David Csejtey</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3.33,53</t>
+          <t>3.31,88</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2151,33 +2151,68 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Paal Aagaard</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3.33,53</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>125</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>08.04.2016</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Njål Høie</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>3.38,05</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C51" t="n">
         <v>117</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>09.03.2014</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Molde</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2194,7 +2229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2832,25 +2867,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.47,88</t>
+          <t>2.44,43</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15.06.2014</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2867,25 +2902,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sondre Brunvoll Møllerløkken</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.49,11</t>
+          <t>2.47,16</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16.06.2024</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ankerskogen svømmehall</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2902,25 +2937,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Einar Woldseth</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2.51,31</t>
+          <t>2.47,88</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16.06.2024</t>
+          <t>15.06.2014</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ankerskogen svømmehall</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2937,16 +2972,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Sondre Brunvoll Møllerløkken</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.52,25</t>
+          <t>2.49,11</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,25 +3007,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bjarne Forfot</t>
+          <t>Einar Woldseth</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.52,31</t>
+          <t>2.51,31</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08.07.2017</t>
+          <t>16.06.2024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ankerskogen svømmehall</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3007,25 +3042,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ole Skuseth</t>
+          <t>Bjarne Forfot</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2.58,88</t>
+          <t>2.52,31</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>16.06.2024</t>
+          <t>08.07.2017</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ankerskogen svømmehall</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3042,25 +3077,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.59,18</t>
+          <t>2.52,25</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>15.06.2025</t>
+          <t>16.06.2024</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Ankerskogen svømmehall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3077,25 +3112,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Ole Skuseth</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2.59,55</t>
+          <t>2.58,88</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15.06.2025</t>
+          <t>16.06.2024</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Ankerskogen svømmehall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3279,6 +3314,111 @@
         </is>
       </c>
       <c r="G31" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ingeborg Strandenes</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3.34,60</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>182</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Eirik Hamnes Ulriksen</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3.16,27</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>177</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Jesper Julius Sundseth Skjærli</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4.03,46</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>93</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3295,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3933,20 +4073,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Irja Gravdahl</t>
+          <t>Helle Johnsen Selsås</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.56,85</t>
+          <t>2.55,90</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11.10.2009</t>
+          <t>07.03.2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3968,20 +4108,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tage Singstad</t>
+          <t>Irja Gravdahl</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.41,81</t>
+          <t>2.56,85</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18.06.2011</t>
+          <t>11.10.2009</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4003,20 +4143,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Maud Steinsdotter Nestgaard</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3.02,32</t>
+          <t>2.59,97</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05.10.2014</t>
+          <t>07.03.2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4038,25 +4178,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cesilie Solberg Jørgensen</t>
+          <t>Tage Singstad</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3.02,77</t>
+          <t>2.41,81</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>28.10.2012</t>
+          <t>18.06.2011</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4073,20 +4213,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mila Maria Flåan</t>
+          <t>Maud Steinsdotter Nestgaard</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3.03,41</t>
+          <t>3.02,32</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>05.10.2014</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4108,25 +4248,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sigrid Eldholm</t>
+          <t>Cesilie Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3.04,76</t>
+          <t>3.02,77</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>03.10.2021</t>
+          <t>28.10.2012</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4143,20 +4283,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Helle Johnsen Selsås</t>
+          <t>Mila Maria Flåan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3.09,09</t>
+          <t>3.03,41</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>28.09.2025</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4178,20 +4318,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Olea Winnberg</t>
+          <t>Sigrid Eldholm</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3.13,18</t>
+          <t>3.04,76</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>03.10.2021</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4213,25 +4353,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Oline Skjønberg</t>
+          <t>Olea Winnberg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3.26,20</t>
+          <t>3.13,18</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4248,25 +4388,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chloe Branlat</t>
+          <t>Oline Skjønberg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3.37,04</t>
+          <t>3.26,20</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4283,20 +4423,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Chloe Branlat</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3.40,13</t>
+          <t>3.37,04</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>06.10.2013</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4318,33 +4458,68 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Othelie Annette Høie</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3.40,13</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>160</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>06.10.2013</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>3.55,64</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C31" t="n">
         <v>130</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>19.01.2025</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Trondheim</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -4361,7 +4536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4894,25 +5069,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Live Killingberg Sandberg</t>
+          <t>Louise Thys</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3.30,29</t>
+          <t>3.29,16</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16.06.2019</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4929,25 +5104,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Irja Gravdahl</t>
+          <t>Live Killingberg Sandberg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3.46,84</t>
+          <t>3.30,29</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29.04.2006</t>
+          <t>16.06.2019</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4964,33 +5139,173 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Irja Gravdahl</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3.46,84</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>154</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>29.04.2006</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Hedda Østgaard</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>3.55,24</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>138</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>29.04.2006</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Namsos</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>50m</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ilaria Kari Cherubini</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4.13,30</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>111</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vilma Granhus Følstad</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4.29,76</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>92</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Aurora Aarflot Johannessen</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4.30,45</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>91</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>07.06.2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
